--- a/Correct Physicians’ Employee IDs in HR Portal.xlsx
+++ b/Correct Physicians’ Employee IDs in HR Portal.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41e5c0185c049b29/Desktop/doctor-portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{2A9844F8-35B7-461F-96D0-D44D9BF0AF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648B9000-8190-490F-A32C-9BF846427CF0}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{2A9844F8-35B7-461F-96D0-D44D9BF0AF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E4EAED2-1C98-4DC5-9EF9-E4FA0CA51539}"/>
   <bookViews>
-    <workbookView xWindow="310" yWindow="10" windowWidth="22730" windowHeight="14630" xr2:uid="{69E36F97-F02A-455D-BDFA-63261E3ABF42}"/>
+    <workbookView xWindow="310" yWindow="10" windowWidth="22730" windowHeight="14630" activeTab="1" xr2:uid="{69E36F97-F02A-455D-BDFA-63261E3ABF42}"/>
   </bookViews>
   <sheets>
     <sheet name="رقم وظيفي - الاستقطاب" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>#</t>
   </si>
@@ -72,13 +73,19 @@
   </si>
   <si>
     <t>الرقم الوظيفي حسب HR Portal</t>
+  </si>
+  <si>
+    <t>طلال مسلط هندي العتيبي</t>
+  </si>
+  <si>
+    <t>بسام حسيان الاقعم العنزي</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +102,17 @@
     <font>
       <sz val="16"/>
       <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF212529"/>
+      <name val="NotoKufiArabic"/>
     </font>
   </fonts>
   <fills count="5">
@@ -147,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +176,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,14 +481,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23DBDF9-D799-410A-8246-2C5992DD08ED}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="32.1640625" customWidth="1"/>
     <col min="3" max="4" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -496,7 +516,7 @@
         <v>91047</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -510,7 +530,7 @@
         <v>91048</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -524,7 +544,7 @@
         <v>91051</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -538,7 +558,7 @@
         <v>91050</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -552,7 +572,7 @@
         <v>91052</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="30" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -566,7 +586,7 @@
         <v>91053</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -583,4 +603,153 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B385C60-185F-4DAD-BD05-D112E76D81E8}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" customWidth="1"/>
+    <col min="3" max="4" width="28.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>91048</v>
+      </c>
+      <c r="D2" s="2">
+        <v>91047</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>91051</v>
+      </c>
+      <c r="D3" s="3">
+        <v>91048</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>91053</v>
+      </c>
+      <c r="D4" s="2">
+        <v>91051</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>91054</v>
+      </c>
+      <c r="D5" s="3">
+        <v>91050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>91044</v>
+      </c>
+      <c r="D6" s="2">
+        <v>91052</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3">
+        <v>91052</v>
+      </c>
+      <c r="D7" s="3">
+        <v>91053</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>91047</v>
+      </c>
+      <c r="D8" s="2">
+        <v>91054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4">
+        <v>91050</v>
+      </c>
+      <c r="D9" s="5">
+        <v>91060</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>91057</v>
+      </c>
+      <c r="D10" s="5">
+        <v>91061</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>